--- a/datas/dataparsing1.xlsx
+++ b/datas/dataparsing1.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robert\Desktop\stirling-engine-measurement\datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robert\Documents\stirling-engine-measurement\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDC1166-D8BD-4DF3-82E5-9A16E0F50E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B40B6A0-84B7-4158-9F1A-2C24051B463D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{0D47C25F-62A5-46FE-A0D6-6163935E984E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{0D47C25F-62A5-46FE-A0D6-6163935E984E}"/>
   </bookViews>
   <sheets>
     <sheet name="frekvencia" sheetId="1" r:id="rId1"/>
     <sheet name="NTCfenti" sheetId="4" r:id="rId2"/>
-    <sheet name="NTCbenti" sheetId="3" r:id="rId3"/>
+    <sheet name="NTClenti" sheetId="3" r:id="rId3"/>
     <sheet name="NTCszobahomerseklet" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -6459,7 +6459,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>

--- a/datas/dataparsing1.xlsx
+++ b/datas/dataparsing1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robert\Documents\stirling-engine-measurement\datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B40B6A0-84B7-4158-9F1A-2C24051B463D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EA9CA67-9422-4DE2-B59F-05D3A75CDEAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{0D47C25F-62A5-46FE-A0D6-6163935E984E}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{0D47C25F-62A5-46FE-A0D6-6163935E984E}"/>
   </bookViews>
   <sheets>
     <sheet name="frekvencia" sheetId="1" r:id="rId1"/>
@@ -7595,7 +7595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCA6E253-76EB-4C1F-B311-8D56CF7BE725}">
-  <dimension ref="A1:D951"/>
+  <dimension ref="A1:D940"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -22639,61 +22639,6 @@
       <c r="D940">
         <f t="shared" si="29"/>
         <v>997.7</v>
-      </c>
-    </row>
-    <row r="941" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A941">
-        <v>47.619050000000001</v>
-      </c>
-    </row>
-    <row r="942" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A942">
-        <v>47.619050000000001</v>
-      </c>
-    </row>
-    <row r="943" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A943">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="944" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A944">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="945" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A945">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="946" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A946">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="947" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A947">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="948" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A948">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="949" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A949">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="950" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A950">
-        <v>45.454543999999999</v>
-      </c>
-    </row>
-    <row r="951" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A951">
-        <v>45.454543999999999</v>
       </c>
     </row>
   </sheetData>
